--- a/modelado/modelos/resultados/Regre/ML_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/ML_reg.xlsx
@@ -201,6 +201,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -429,9 +432,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M18"/>
+  <dimension ref="A2:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -1070,43 +1070,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.538239104781718</v>
+        <v>0.5411667563543621</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7419551512701935</v>
+        <v>0.7435906738930691</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7000100190579657</v>
+        <v>0.7069680505082794</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5223118662834167</v>
+        <v>0.5229051113128662</v>
       </c>
       <c r="E3" t="n">
-        <v>1.769527379435736</v>
+        <v>1.763908890260923</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1776799273971036</v>
+        <v>0.1771157695545838</v>
       </c>
       <c r="G3" t="n">
-        <v>1.215611303069335</v>
+        <v>1.213826105341489</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2510944453239524</v>
+        <v>-0.2420356417895605</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8722400907119032</v>
+        <v>0.8762676892415103</v>
       </c>
       <c r="J3" t="n">
-        <v>0.707596907674348</v>
+        <v>0.7098581157005004</v>
       </c>
       <c r="K3" t="n">
-        <v>54.66666666666666</v>
+        <v>54.77777777777778</v>
       </c>
       <c r="L3" t="n">
-        <v>53.77777777777778</v>
+        <v>53.44444444444445</v>
       </c>
       <c r="M3" t="n">
-        <v>39.5971425971426</v>
+        <v>39.73327873327874</v>
       </c>
     </row>
     <row r="5">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.181638260000982</v>
+        <v>0.2309413688698807</v>
       </c>
     </row>
     <row r="7">
@@ -1138,117 +1138,97 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1269288736220613</v>
+        <v>0.171228224401637</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1216337697377634</v>
+        <v>0.08831843475084321</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>to_b</t>
+          <t>zo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07318690598729671</v>
+        <v>0.08787640414945988</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>zo</t>
+          <t>so</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07316395482232359</v>
+        <v>0.07849089944923124</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06995518865168066</v>
+        <v>0.07825053342186693</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>so</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06868380715782549</v>
+        <v>0.07788548870716371</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06832863485067969</v>
+        <v>0.07290533310635772</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>moon_phase</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06476465698406758</v>
+        <v>0.0565578970725043</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05843085147159649</v>
+        <v>0.0308771814025048</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>moon_phase</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05132317594167589</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>month_cos</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.02126666831829442</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>month_sin</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.02069525245375285</v>
+        <v>0.02666823466855049</v>
       </c>
     </row>
   </sheetData>
@@ -1335,43 +1315,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5369115362524649</v>
+        <v>0.5407543743895306</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7391161287886026</v>
+        <v>0.741643706749687</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7189449186549566</v>
+        <v>0.7253871499020876</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5237712860107422</v>
+        <v>0.5266227126121521</v>
       </c>
       <c r="E3" t="n">
-        <v>1.772069260780653</v>
+        <v>1.764701379532983</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1779351601208611</v>
+        <v>0.1771953441562311</v>
       </c>
       <c r="G3" t="n">
-        <v>1.199204469012751</v>
+        <v>1.190404268690813</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2354121350041396</v>
+        <v>-0.2337257187325176</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8316560804083115</v>
+        <v>0.8243930792182336</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7060830277074993</v>
+        <v>0.7081078011092283</v>
       </c>
       <c r="K3" t="n">
-        <v>53.55555555555556</v>
+        <v>53.44444444444445</v>
       </c>
       <c r="L3" t="n">
-        <v>53.66666666666666</v>
+        <v>52.44444444444445</v>
       </c>
       <c r="M3" t="n">
-        <v>38.75623557441739</v>
+        <v>39.20068001886184</v>
       </c>
     </row>
   </sheetData>
@@ -1458,43 +1438,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5044501252071206</v>
+        <v>0.4960422502213112</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7220710977411036</v>
+        <v>0.7159247558795725</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6512854819173254</v>
+        <v>0.6258950341182961</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4994775056838989</v>
+        <v>0.4961459338665009</v>
       </c>
       <c r="E3" t="n">
-        <v>1.833126334261229</v>
+        <v>1.848612030809468</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1840659589483807</v>
+        <v>0.1856208924692522</v>
       </c>
       <c r="G3" t="n">
-        <v>1.242943953478232</v>
+        <v>1.262662105787305</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3249899558999704</v>
+        <v>-0.3209164058288301</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8831992900009409</v>
+        <v>0.8992109851152228</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6941061187657019</v>
+        <v>0.6898618144655836</v>
       </c>
       <c r="K3" t="n">
         <v>54.66666666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>54.33333333333334</v>
+        <v>54.11111111111111</v>
       </c>
       <c r="M3" t="n">
-        <v>39.84438984438984</v>
+        <v>39.62216762216762</v>
       </c>
     </row>
   </sheetData>
@@ -2399,7 +2379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M18"/>
+  <dimension ref="A2:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -2471,43 +2451,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4020588994026184</v>
+        <v>0.3952797651290894</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6587373018264771</v>
+        <v>0.6550655364990234</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6771655477757782</v>
+        <v>0.6655108063010973</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4561565816402435</v>
+        <v>0.4522053301334381</v>
       </c>
       <c r="E3" t="n">
-        <v>2.013621791213061</v>
+        <v>2.025004247967067</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2021896794736517</v>
+        <v>0.2033326027836586</v>
       </c>
       <c r="G3" t="n">
-        <v>1.38087272644043</v>
+        <v>1.390760660171509</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2925567328929901</v>
+        <v>-0.3026900589466095</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7986968679954815</v>
+        <v>0.8034435019837692</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6258356991043701</v>
+        <v>0.6220680941536283</v>
       </c>
       <c r="K3" t="n">
-        <v>49.66666666666666</v>
+        <v>49.55555555555556</v>
       </c>
       <c r="L3" t="n">
-        <v>49.33333333333334</v>
+        <v>49.11111111111111</v>
       </c>
       <c r="M3" t="n">
-        <v>38.00348282166465</v>
+        <v>37.8673466855285</v>
       </c>
     </row>
     <row r="5">
@@ -2539,10 +2519,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4194623655913978</v>
+        <v>0.4225806451612903</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1140714660286903</v>
+        <v>0.1498491764068604</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2557,10 +2537,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1128494623655914</v>
+        <v>0.1109677419354839</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01771104335784912</v>
+        <v>0.02190171740949154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2575,10 +2555,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1398924731182796</v>
+        <v>0.137741935483871</v>
       </c>
       <c r="C8" t="n">
-        <v>0.060357466340065</v>
+        <v>0.0745202824473381</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2589,50 +2569,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>to_b</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2906989247311828</v>
+        <v>0.1481182795698925</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0479038842022419</v>
+        <v>0.1903441250324249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Positive (+)</t>
+          <t>Negative (-)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1487096774193548</v>
+        <v>0.1334408602150538</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1543295979499817</v>
+        <v>0.1411238312721252</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Negative (-)</t>
+          <t>Positive (+)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1320967741935484</v>
+        <v>0.1981720430107527</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1132164895534515</v>
+        <v>0.2600504159927368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2643,14 +2623,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2150537634408602</v>
+        <v>0.1508602150537634</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2132931798696518</v>
+        <v>0.3937568068504333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2661,106 +2641,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1448924731182796</v>
+        <v>0.1829569892473118</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3219575583934784</v>
+        <v>0.4379396438598633</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Negative (-)</t>
+          <t>Positive (+)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1773655913978495</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3464913666248322</v>
+        <v>0.05457955971360207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Positive (+)</t>
+          <t>Negative (-)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1887096774193548</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2751836776733398</v>
+        <v>0.05457955598831177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Positive (+)</t>
+          <t>Negative (-)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>moon_phase</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04888107627630234</v>
+        <v>0.1568818092346191</v>
       </c>
       <c r="D16" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>month_cos</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.04888107627630234</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Positive (+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>moon_phase</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.1457557827234268</v>
-      </c>
-      <c r="D18" t="inlineStr">
         <is>
           <t>Positive (+)</t>
         </is>

--- a/modelado/modelos/resultados/Regre/ML_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/ML_reg.xlsx
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M13"/>
+  <dimension ref="A2:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -779,43 +779,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5453104743302623</v>
+        <v>0.5358631341969944</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7464788802918561</v>
+        <v>0.7460574240255258</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7178208542170876</v>
+        <v>0.6854011642191697</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5249535441398621</v>
+        <v>0.5232681632041931</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7559259049284</v>
+        <v>1.778443246313423</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1763141904036881</v>
+        <v>0.1516402567077832</v>
       </c>
       <c r="G3" t="n">
-        <v>1.202687214128028</v>
+        <v>1.220502410408639</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2456014992457628</v>
+        <v>-0.3281657365289745</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8672631719487408</v>
+        <v>0.8946860406994075</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7123299880911111</v>
+        <v>0.7141099365179543</v>
       </c>
       <c r="K3" t="n">
-        <v>54.55555555555556</v>
+        <v>54.66666666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>54</v>
+        <v>53.11111111111111</v>
       </c>
       <c r="M3" t="n">
-        <v>40.17772317772318</v>
+        <v>39.84438984438984</v>
       </c>
     </row>
     <row r="5">
@@ -837,77 +837,107 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2818870083289323</v>
+        <v>0.1852468144816836</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>so</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1840930879682992</v>
+        <v>0.1253841190767289</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1197900870567105</v>
+        <v>0.1247355404975009</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1191265403278294</v>
+        <v>0.1116648637935136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1169908913532578</v>
+        <v>0.08383177331195397</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>so</t>
+          <t>zo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1144204191548788</v>
+        <v>0.08340292568102782</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03306461190415213</v>
+        <v>0.07983652282399248</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.07812815234053268</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ugo</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.07735659303479801</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>month_cos</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.02541288816592193</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>month_sin</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0.03062735390594005</v>
+      <c r="B16" t="n">
+        <v>0.02499980679234612</v>
       </c>
     </row>
   </sheetData>
@@ -994,43 +1024,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5357245607854069</v>
+        <v>0.5358332827185683</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7380488148763753</v>
+        <v>0.7440380395275106</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7155198638685027</v>
+        <v>0.7093990117510554</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5238391160964966</v>
+        <v>0.527459442615509</v>
       </c>
       <c r="E3" t="n">
-        <v>1.774338866678667</v>
+        <v>1.778500436670962</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1781630534079985</v>
+        <v>0.1516451330852085</v>
       </c>
       <c r="G3" t="n">
-        <v>1.199292981085959</v>
+        <v>1.204780570203797</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2327880680562556</v>
+        <v>-0.3163165230296738</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8256293211040067</v>
+        <v>0.8611983600591722</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7054888948399576</v>
+        <v>0.7117896084436554</v>
       </c>
       <c r="K3" t="n">
-        <v>54.33333333333334</v>
+        <v>53.88888888888889</v>
       </c>
       <c r="L3" t="n">
-        <v>52.77777777777778</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="M3" t="n">
-        <v>39.15269815269815</v>
+        <v>38.3999453999454</v>
       </c>
     </row>
   </sheetData>
@@ -1117,43 +1147,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5090005676965679</v>
+        <v>0.5094381842701934</v>
       </c>
       <c r="B3" t="n">
-        <v>0.72553168376486</v>
+        <v>0.7304655950861517</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6584685017530387</v>
+        <v>0.64738229368058</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5004421472549438</v>
+        <v>0.508537232875824</v>
       </c>
       <c r="E3" t="n">
-        <v>1.824690479379189</v>
+        <v>1.828368995861875</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1832189067352347</v>
+        <v>0.1558972120497933</v>
       </c>
       <c r="G3" t="n">
-        <v>1.229679505816736</v>
+        <v>1.215518599713779</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3316542037668357</v>
+        <v>-0.3930789053790416</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8683386095504166</v>
+        <v>0.867029773333921</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6976478854331718</v>
+        <v>0.7034600291970164</v>
       </c>
       <c r="K3" t="n">
-        <v>54.77777777777778</v>
+        <v>53.77777777777778</v>
       </c>
       <c r="L3" t="n">
-        <v>53.55555555555556</v>
+        <v>52.55555555555556</v>
       </c>
       <c r="M3" t="n">
-        <v>40.17565499383682</v>
+        <v>39.09163709163709</v>
       </c>
     </row>
   </sheetData>
@@ -1918,7 +1948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M13"/>
+  <dimension ref="A2:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -1990,43 +2020,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.462360143661499</v>
+        <v>0.4394358992576599</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6912532448768616</v>
+        <v>0.678267776966095</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7171527800088057</v>
+        <v>0.6906553268084225</v>
       </c>
       <c r="D3" t="n">
-        <v>0.482560783624649</v>
+        <v>0.4747259914875031</v>
       </c>
       <c r="E3" t="n">
-        <v>1.909389037534867</v>
+        <v>1.954472801559887</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1917235695274765</v>
+        <v>0.1666495447472321</v>
       </c>
       <c r="G3" t="n">
-        <v>1.310649275779724</v>
+        <v>1.339357018470764</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2516731917858124</v>
+        <v>-0.287206768989563</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7984093977895875</v>
+        <v>0.8121235032534848</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6628197213194666</v>
+        <v>0.6503072990387481</v>
       </c>
       <c r="K3" t="n">
-        <v>52.44444444444445</v>
+        <v>52</v>
       </c>
       <c r="L3" t="n">
-        <v>52.55555555555556</v>
+        <v>50.77777777777778</v>
       </c>
       <c r="M3" t="n">
-        <v>37.64926083107901</v>
+        <v>39.05353287171469</v>
       </c>
     </row>
     <row r="5">
@@ -2058,10 +2088,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2625268817204301</v>
+        <v>0.2618817204301075</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1747564077377319</v>
+        <v>0.1320142894983292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2076,10 +2106,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1225806451612903</v>
+        <v>0.373010752688172</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01154964044690132</v>
+        <v>0.0118409302085638</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2090,32 +2120,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>zo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1591935483870968</v>
+        <v>0.2677956989247312</v>
       </c>
       <c r="C8" t="n">
-        <v>0.266091376543045</v>
+        <v>0.1221202611923218</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Negative (-)</t>
+          <t>Positive (+)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1620967741935484</v>
+        <v>0.1511290322580645</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3633047342300415</v>
+        <v>0.1930740177631378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2126,14 +2156,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2018279569892473</v>
+        <v>0.164247311827957</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4145779013633728</v>
+        <v>0.2661277651786804</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2144,14 +2174,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1760215053763441</v>
+        <v>0.2302688172043011</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5312507748603821</v>
+        <v>0.3355251252651215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2162,14 +2192,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3093010752688172</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06792637705802917</v>
+        <v>0.4287397861480713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2180,18 +2210,72 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.1679032258064516</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3490584790706635</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1818279569892473</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.2653153538703918</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>month_sin</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0332786813378334</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>month_cos</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.06792637705802917</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Positive (+)</t>
+      <c r="B16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0332786813378334</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
         </is>
       </c>
     </row>

--- a/modelado/modelos/resultados/Regre/ML_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/ML_reg.xlsx
@@ -15,6 +15,8 @@
     <sheet name="KNeighborsRegressor_SQA" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Ridge_SQA" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Ridge_HKP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="RandomForestRegressor_HKP_todas" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Ridge_HKP_ALL" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -167,6 +169,39 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9534525" cy="3724275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -420,6 +455,39 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9534525" cy="3724275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -701,13 +769,769 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:M22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>hit_rate_percent</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>mean_yearly_hit_rate</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>mean_monthly_hit_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5442202468595931</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7498002689820007</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7155016411887738</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5289776921272278</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.762359452940867</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1502688603694941</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.202577193823403</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.3048534492510599</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8764373183136145</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7169331406053284</v>
+      </c>
+      <c r="K3" t="n">
+        <v>54.55555555555556</v>
+      </c>
+      <c r="L3" t="n">
+        <v>52.88888888888889</v>
+      </c>
+      <c r="M3" t="n">
+        <v>38.17772317772318</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1730896101735321</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1052595003667529</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mlotst</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.09907396419579709</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>so</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.07585621718033544</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>to_b</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.07568422313718813</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.07459887329895339</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.06567923615057956</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>zo</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.06425200277086549</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0629704105721325</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>vgo</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.06116813215044469</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ugo</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.05712301548744142</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>moon_phase</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.04541555064381098</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>month_cos</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.01996283897235526</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>month_sin</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.01986642489981091</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>lon</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:M22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>hit_rate_percent</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>mean_yearly_hit_rate</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>mean_monthly_hit_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.3854799270629883</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6573387384414673</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7838290376596155</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4801674485206604</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.046374077690764</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1744855738885315</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.426749348640442</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0627472847700119</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7279549123926295</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6316953569823175</v>
+      </c>
+      <c r="K3" t="n">
+        <v>48.55555555555556</v>
+      </c>
+      <c r="L3" t="n">
+        <v>47.55555555555556</v>
+      </c>
+      <c r="M3" t="n">
+        <v>36.60908842727024</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Significant_Grid_Ratio</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Overall_Impact</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1701612903225806</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1099733114242554</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>so</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1606989247311828</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.007503432687371969</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>zo</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.05940860215053764</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.08029704540967941</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>to_b</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3378494623655914</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.07654603570699692</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>vgo</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1121505376344086</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1608383357524872</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ugo</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1217741935483871</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2197796404361725</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mlotst</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2341935483870968</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.303412914276123</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2012903225806452</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3471009433269501</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1774731182795699</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.3142023086547852</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.190752688172043</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.2422534972429276</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>month_sin</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.02860867977142334</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>month_cos</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.02860867790877819</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.05961307883262634</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>moon_phase</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.1183258220553398</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>8.897072234503867e-08</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>lon</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>9.044158133519886e-08</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>8.766466663701067e-08</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M16"/>
+  <dimension ref="A2:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -776,46 +1600,54 @@
           <t>mean_monthly_hit_rate</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>val_r2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5358631341969944</v>
+        <v>0.5173675082777789</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7460574240255258</v>
+        <v>0.7578703810206018</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6854011642191697</v>
+        <v>0.4826738493610659</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5232681632041931</v>
+        <v>0.502981960773468</v>
       </c>
       <c r="E3" t="n">
-        <v>1.778443246313423</v>
+        <v>1.904327931889335</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1516402567077832</v>
+        <v>0.1947918766936014</v>
       </c>
       <c r="G3" t="n">
-        <v>1.220502410408639</v>
+        <v>1.321373478588611</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3281657365289745</v>
+        <v>-0.5677882208851476</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8946860406994075</v>
+        <v>1.061260413258312</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7141099365179543</v>
+        <v>0.7197255047219923</v>
       </c>
       <c r="K3" t="n">
-        <v>54.66666666666666</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>53.11111111111111</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>39.84438984438984</v>
+        <v>34.68468468468468</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5528688855898922</v>
       </c>
     </row>
     <row r="5">
@@ -837,107 +1669,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1852468144816836</v>
+        <v>0.2747600689837364</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>so</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1253841190767289</v>
+        <v>0.1933678796278239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1247355404975009</v>
+        <v>0.1800818287535049</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1116648637935136</v>
+        <v>0.1451883060851044</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08383177331195397</v>
+        <v>0.1389502834593309</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>zo</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08340292568102782</v>
+        <v>0.0340271582768049</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07983652282399248</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CHL</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.07812815234053268</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ugo</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.07735659303479801</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>month_cos</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.02541288816592193</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>month_sin</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.02499980679234612</v>
+        <v>0.03362447481369475</v>
       </c>
     </row>
   </sheetData>
@@ -1024,43 +1816,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5358332827185683</v>
+        <v>0.5169064720072285</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7440380395275106</v>
+        <v>0.7585995926560705</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7093990117510554</v>
+        <v>0.4908296679578035</v>
       </c>
       <c r="D3" t="n">
-        <v>0.527459442615509</v>
+        <v>0.5024036765098572</v>
       </c>
       <c r="E3" t="n">
-        <v>1.778500436670962</v>
+        <v>1.905237272529682</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1516451330852085</v>
+        <v>0.1948848922750677</v>
       </c>
       <c r="G3" t="n">
-        <v>1.204780570203797</v>
+        <v>1.306908830749982</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3163165230296738</v>
+        <v>-0.5901875208353563</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8611983600591722</v>
+        <v>1.044515209701142</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7117896084436554</v>
+        <v>0.7219167655314058</v>
       </c>
       <c r="K3" t="n">
-        <v>53.88888888888889</v>
+        <v>47</v>
       </c>
       <c r="L3" t="n">
-        <v>52.66666666666666</v>
+        <v>47</v>
       </c>
       <c r="M3" t="n">
-        <v>38.3999453999454</v>
+        <v>34.75975975975976</v>
       </c>
     </row>
   </sheetData>
@@ -1147,43 +1939,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5094381842701934</v>
+        <v>0.5037967521181721</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7304655950861517</v>
+        <v>0.7476911206978047</v>
       </c>
       <c r="C3" t="n">
-        <v>0.64738229368058</v>
+        <v>0.4814770249423352</v>
       </c>
       <c r="D3" t="n">
-        <v>0.508537232875824</v>
+        <v>0.4915917813777924</v>
       </c>
       <c r="E3" t="n">
-        <v>1.828368995861875</v>
+        <v>1.930915464478814</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1558972120497933</v>
+        <v>0.1975114898878577</v>
       </c>
       <c r="G3" t="n">
-        <v>1.215518599713779</v>
+        <v>1.298503291171964</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3930789053790416</v>
+        <v>-0.5968345033118563</v>
       </c>
       <c r="I3" t="n">
-        <v>0.867029773333921</v>
+        <v>1.034418863846348</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7034600291970164</v>
+        <v>0.7145176856195021</v>
       </c>
       <c r="K3" t="n">
-        <v>53.77777777777778</v>
+        <v>47</v>
       </c>
       <c r="L3" t="n">
-        <v>52.55555555555556</v>
+        <v>47</v>
       </c>
       <c r="M3" t="n">
-        <v>39.09163709163709</v>
+        <v>34.01801801801802</v>
       </c>
     </row>
   </sheetData>
@@ -1198,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M13"/>
+  <dimension ref="A2:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -1270,43 +2062,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.436505437732344</v>
+        <v>0.4239686877513599</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6664985855151144</v>
+        <v>0.6561383555925686</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7873029136021311</v>
+        <v>0.7759336260943714</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3868452906608582</v>
+        <v>0.4022642374038696</v>
       </c>
       <c r="E3" t="n">
-        <v>1.263861515288427</v>
+        <v>1.284249405236245</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09705233331593402</v>
+        <v>0.09861792595950197</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7477991567707717</v>
+        <v>0.7460346226224139</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1139354753070746</v>
+        <v>-0.09740234138441493</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4562373864096569</v>
+        <v>0.4802822290250827</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5854760880968078</v>
+        <v>0.5941096738544712</v>
       </c>
       <c r="K3" t="n">
-        <v>64.77777777777777</v>
+        <v>64.33333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>65.1111111111111</v>
+        <v>64.44444444444444</v>
       </c>
       <c r="M3" t="n">
-        <v>34.59612357884608</v>
+        <v>30.36410264933322</v>
       </c>
     </row>
     <row r="5">
@@ -1328,7 +2120,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2895804554554137</v>
+        <v>0.2655933461888232</v>
       </c>
     </row>
     <row r="7">
@@ -1338,7 +2130,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2235035953652346</v>
+        <v>0.2498551626693538</v>
       </c>
     </row>
     <row r="8">
@@ -1348,57 +2140,47 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1176437221834511</v>
+        <v>0.1551216285896718</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1068573964201792</v>
+        <v>0.1398533618117629</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.100376037540246</v>
+        <v>0.1377725298054446</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>so</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.09522686571186335</v>
+        <v>0.03077208364856796</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03549491745617884</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>month_sin</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.03131700986743328</v>
+        <v>0.02103188728637541</v>
       </c>
     </row>
   </sheetData>
@@ -1485,43 +2267,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4337435939984541</v>
+        <v>0.4096632260453719</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6622591510814975</v>
+        <v>0.64318496770858</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7844682870977794</v>
+        <v>0.7489018891565367</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4055547714233398</v>
+        <v>0.4005488753318787</v>
       </c>
       <c r="E3" t="n">
-        <v>1.266954997997612</v>
+        <v>1.300098467131428</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09728988285072644</v>
+        <v>0.09983498053327389</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7317634244407286</v>
+        <v>0.7385428359545111</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1094335916416725</v>
+        <v>-0.1005368884018129</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4408125097625338</v>
+        <v>0.4553512309788286</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6016115064605859</v>
+        <v>0.5741879775451267</v>
       </c>
       <c r="K3" t="n">
-        <v>65.11111111111111</v>
+        <v>63.55555555555556</v>
       </c>
       <c r="L3" t="n">
-        <v>65.22222222222221</v>
+        <v>63.44444444444444</v>
       </c>
       <c r="M3" t="n">
-        <v>35.10069499369317</v>
+        <v>31.58023602204054</v>
       </c>
     </row>
   </sheetData>
@@ -1608,43 +2390,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4261363288163195</v>
+        <v>0.4168729008931139</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6537793834058381</v>
+        <v>0.6473475025736835</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8146203486789917</v>
+        <v>0.79889737979831</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3854392468929291</v>
+        <v>0.4019865989685059</v>
       </c>
       <c r="E3" t="n">
-        <v>1.275436940085797</v>
+        <v>1.292135146621226</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09794121391884682</v>
+        <v>0.09922347458336662</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7454770331000299</v>
+        <v>0.7458760803199844</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06048505532531309</v>
+        <v>-0.07690508539921211</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4331208216862568</v>
+        <v>0.4455049419331603</v>
       </c>
       <c r="J3" t="n">
-        <v>0.571930323273936</v>
+        <v>0.5667574044461284</v>
       </c>
       <c r="K3" t="n">
-        <v>62.66666666666667</v>
+        <v>63.88888888888889</v>
       </c>
       <c r="L3" t="n">
-        <v>62.77777777777777</v>
+        <v>64</v>
       </c>
       <c r="M3" t="n">
-        <v>41.47028012505346</v>
+        <v>42.59934440615084</v>
       </c>
     </row>
   </sheetData>
@@ -1659,7 +2441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M13"/>
+  <dimension ref="A2:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -1731,43 +2513,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.3395151495933533</v>
+        <v>0.2886205911636353</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5969511270523071</v>
+        <v>0.5599545240402222</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7621407754283389</v>
+        <v>0.7022079077214785</v>
       </c>
       <c r="D3" t="n">
-        <v>0.269804060459137</v>
+        <v>0.2666338682174683</v>
       </c>
       <c r="E3" t="n">
-        <v>1.368314877678719</v>
+        <v>1.427174177782105</v>
       </c>
       <c r="F3" t="n">
-        <v>0.10507334069692</v>
+        <v>0.1095931653321948</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8930536508560181</v>
+        <v>0.9324483275413513</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1134928837418556</v>
+        <v>-0.0796208530664444</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5022119747104072</v>
+        <v>0.5056556946677155</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4830197399097944</v>
+        <v>0.4647540018532914</v>
       </c>
       <c r="K3" t="n">
-        <v>60.66666666666667</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="L3" t="n">
-        <v>61</v>
+        <v>57.11111111111111</v>
       </c>
       <c r="M3" t="n">
-        <v>31.21364638685951</v>
+        <v>30.49133429253847</v>
       </c>
     </row>
     <row r="5">
@@ -1799,10 +2581,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3648387096774194</v>
+        <v>0.3154301075268817</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2472736984491348</v>
+        <v>0.297783374786377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1813,50 +2595,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>so</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2980107526881721</v>
+        <v>0.2151075268817204</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01640017330646515</v>
+        <v>0.4146672487258911</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Positive (+)</t>
+          <t>Negative (-)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2301075268817204</v>
+        <v>0.1934408602150538</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3388948738574982</v>
+        <v>0.5518999695777893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Negative (-)</t>
+          <t>Positive (+)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1994086021505376</v>
+        <v>0.2033333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4210817813873291</v>
+        <v>0.5607455372810364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1867,32 +2649,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2119892473118279</v>
+        <v>0.1620967741935484</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4604678750038147</v>
+        <v>0.7183315753936768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Positive (+)</t>
+          <t>Negative (-)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1604838709677419</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5589300990104675</v>
+        <v>0.1275649219751358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1903,36 +2685,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.8333333333333334</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1479589343070984</v>
+        <v>0.1275649070739746</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Negative (-)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>month_cos</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.1479589343070984</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Positive (+)</t>
         </is>
       </c>
     </row>
@@ -1948,7 +2712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M16"/>
+  <dimension ref="A2:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -2020,43 +2784,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4394358992576599</v>
+        <v>0.4662400484085083</v>
       </c>
       <c r="B3" t="n">
-        <v>0.678267776966095</v>
+        <v>0.6969954371452332</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6906553268084225</v>
+        <v>0.6510942185495402</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4747259914875031</v>
+        <v>0.4878996610641479</v>
       </c>
       <c r="E3" t="n">
-        <v>1.954472801559887</v>
+        <v>2.002656483721252</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1666495447472321</v>
+        <v>0.2048498099009879</v>
       </c>
       <c r="G3" t="n">
-        <v>1.339357018470764</v>
+        <v>1.381198883056641</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.287206768989563</v>
+        <v>-0.3562632501125336</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8121235032534848</v>
+        <v>0.9261806139163673</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6503072990387481</v>
+        <v>0.6606190628956702</v>
       </c>
       <c r="K3" t="n">
-        <v>52</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="L3" t="n">
-        <v>50.77777777777778</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="M3" t="n">
-        <v>39.05353287171469</v>
+        <v>32.16816816816817</v>
       </c>
     </row>
     <row r="5">
@@ -2088,10 +2852,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2618817204301075</v>
+        <v>0.2679569892473118</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1320142894983292</v>
+        <v>0.2257164120674133</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2102,68 +2866,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>so</t>
+          <t>vgo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.373010752688172</v>
+        <v>0.1528494623655914</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0118409302085638</v>
+        <v>0.3475975394248962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Negative (-)</t>
+          <t>Positive (+)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>zo</t>
+          <t>ugo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2677956989247312</v>
+        <v>0.1684408602150538</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1221202611923218</v>
+        <v>0.4798481464385986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Positive (+)</t>
+          <t>Negative (-)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>mlotst</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1511290322580645</v>
+        <v>0.2213978494623656</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1930740177631378</v>
+        <v>0.5326579213142395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Positive (+)</t>
+          <t>Negative (-)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.164247311827957</v>
+        <v>0.2464516129032258</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2661277651786804</v>
+        <v>0.6727367043495178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2174,14 +2938,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>month_sin</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2302688172043011</v>
+        <v>0.5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3355251252651215</v>
+        <v>0.06287206709384918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2192,88 +2956,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>month_cos</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3093010752688172</v>
+        <v>0.5</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4287397861480713</v>
+        <v>0.06287205964326859</v>
       </c>
       <c r="D12" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CHL</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.1679032258064516</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.3490584790706635</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Positive (+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.1818279569892473</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.2653153538703918</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Positive (+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>month_sin</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.0332786813378334</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Positive (+)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>month_cos</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.0332786813378334</v>
-      </c>
-      <c r="D16" t="inlineStr">
         <is>
           <t>Negative (-)</t>
         </is>

--- a/modelado/modelos/resultados/Regre/ML_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/ML_reg.xlsx
@@ -17,6 +17,8 @@
     <sheet name="Ridge_HKP" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="RandomForestRegressor_HKP_todas" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Ridge_HKP_ALL" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="RandomForestRegressor_SQA_todas" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Ridge_SQA_ALL" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -234,6 +236,72 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9648825" cy="3724275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9648825" cy="3724275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -422,9 +490,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -455,6 +520,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -775,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M22"/>
+  <dimension ref="A2:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -844,46 +912,54 @@
           <t>mean_monthly_hit_rate</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>val_r2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5442202468595931</v>
+        <v>0.5437706191077546</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7498002689820007</v>
+        <v>0.7623463588108532</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7155016411887738</v>
+        <v>0.5893367607274251</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5289776921272278</v>
+        <v>0.5226950645446777</v>
       </c>
       <c r="E3" t="n">
-        <v>1.762359452940867</v>
+        <v>1.851505832777979</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1502688603694941</v>
+        <v>0.1893887548654255</v>
       </c>
       <c r="G3" t="n">
-        <v>1.202577193823403</v>
+        <v>1.294191317671767</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3048534492510599</v>
+        <v>-0.4459321997519396</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8764373183136145</v>
+        <v>1.017437173583874</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7169331406053284</v>
+        <v>0.7210728319947218</v>
       </c>
       <c r="K3" t="n">
-        <v>54.55555555555556</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="L3" t="n">
-        <v>52.88888888888889</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="M3" t="n">
-        <v>38.17772317772318</v>
+        <v>34.0930930930931</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5486377622286934</v>
       </c>
     </row>
     <row r="5">
@@ -901,81 +977,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1730896101735321</v>
+        <v>0.1553807436094873</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1052595003667529</v>
+        <v>0.09254771847253562</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09907396419579709</v>
+        <v>0.08368350790522039</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>so</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07585621718033544</v>
+        <v>0.07188629422566326</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>to_b</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07568422313718813</v>
+        <v>0.07175178428848725</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>TOB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07459887329895339</v>
+        <v>0.06551931522908375</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>Año</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06567923615057956</v>
+        <v>0.06524255394161993</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zo</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06425200277086549</v>
+        <v>0.05638299479343627</v>
       </c>
     </row>
     <row r="14">
@@ -985,86 +1061,106 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0629704105721325</v>
+        <v>0.05632904511395507</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06116813215044469</v>
+        <v>0.05342073724022577</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>ZSD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05712301548744142</v>
+        <v>0.05340122500158781</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>moon_phase</t>
+          <t>ZO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.04541555064381098</v>
+        <v>0.05256430823234356</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.01996283897235526</v>
+        <v>0.05227643900599604</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.01986642489981091</v>
+        <v>0.03617041674554787</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.01752126414881583</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>lon</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.0159216520459944</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>depth</t>
+          <t>LAT</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LON</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PROF</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1080,7 +1176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M22"/>
+  <dimension ref="A2:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -1152,43 +1248,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.3854799270629883</v>
+        <v>0.410413920879364</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6573387384414673</v>
+        <v>0.6687150001525879</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7838290376596155</v>
+        <v>0.7680133828694716</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4801674485206604</v>
+        <v>0.4923566281795502</v>
       </c>
       <c r="E3" t="n">
-        <v>2.046374077690764</v>
+        <v>2.104781850896206</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1744855738885315</v>
+        <v>0.2152961157062574</v>
       </c>
       <c r="G3" t="n">
-        <v>1.426749348640442</v>
+        <v>1.473315477371216</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0627472847700119</v>
+        <v>0.01311923190951347</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7279549123926295</v>
+        <v>0.8240744994357229</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6316953569823175</v>
+        <v>0.6285678243551241</v>
       </c>
       <c r="K3" t="n">
-        <v>48.55555555555556</v>
+        <v>40.66666666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>47.55555555555556</v>
+        <v>40.66666666666666</v>
       </c>
       <c r="M3" t="n">
-        <v>36.60908842727024</v>
+        <v>32.5015015015015</v>
       </c>
     </row>
     <row r="5">
@@ -1199,324 +1295,1180 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Overall_Impact</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>Significant_Grid_Ratio</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Overall_Impact</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Direction</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1701612903225806</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.1099733114242554</v>
-      </c>
-      <c r="D6" t="inlineStr">
+        <v>0.1522277742624283</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Negative (-)</t>
         </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1546236559139785</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>so</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1606989247311828</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.007503432687371969</v>
-      </c>
-      <c r="D7" t="inlineStr">
+        <v>0.1380684971809387</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Negative (-)</t>
         </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2153763440860215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>zo</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05940860215053764</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.08029704540967941</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Positive (+)</t>
-        </is>
+        <v>0.1253336071968079</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2788709677419355</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>to_b</t>
+          <t>ZSD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3378494623655914</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.07654603570699692</v>
-      </c>
-      <c r="D9" t="inlineStr">
+        <v>0.1246607527136803</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Positive (+)</t>
         </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1811290322580645</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1121505376344086</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.1608383357524872</v>
-      </c>
-      <c r="D10" t="inlineStr">
+        <v>0.121737614274025</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Negative (-)</t>
         </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1788172043010753</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1217741935483871</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.2197796404361725</v>
-      </c>
-      <c r="D11" t="inlineStr">
+        <v>0.09494458138942719</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Negative (-)</t>
         </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1981720430107527</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2341935483870968</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.303412914276123</v>
-      </c>
-      <c r="D12" t="inlineStr">
+        <v>0.08851733803749084</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Negative (-)</t>
         </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1256989247311828</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2012903225806452</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.3471009433269501</v>
-      </c>
-      <c r="D13" t="inlineStr">
+        <v>0.06308501958847046</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Negative (-)</t>
         </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1048924731182796</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1774731182795699</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.3142023086547852</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.04497684165835381</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.190752688172043</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.2422534972429276</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.04405104741454124</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2255913978494624</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>ZO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.02860867977142334</v>
-      </c>
-      <c r="D16" t="inlineStr">
+        <v>0.0364149697124958</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Positive (+)</t>
         </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.09075268817204302</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>TOB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.02860867790877819</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.03260248899459839</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3653763440860215</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>Año</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.05961307883262634</v>
-      </c>
-      <c r="D18" t="inlineStr">
+        <v>0.03048357926309109</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Positive (+)</t>
         </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>moon_phase</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.1183258220553398</v>
-      </c>
-      <c r="D19" t="inlineStr">
+        <v>0.02523194067180157</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Positive (+)</t>
         </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>8.897072234503867e-08</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.02523194067180157</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>lon</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>9.044158133519886e-08</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Positive (+)</t>
-        </is>
+        <v>0.004079577513039112</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1663978494623656</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>depth</t>
+          <t>LON</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.795160374518101e-11</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LAT</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.592097634284251e-11</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PROF</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.507163664704603e-11</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:N24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>hit_rate_percent</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>mean_yearly_hit_rate</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>mean_monthly_hit_rate</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>val_r2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.4884697310920645</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7053124597322105</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8582397138708936</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3940118849277496</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.267680895391697</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1102405446830854</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7474148510863977</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.08042096524278439</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4630084649753027</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6165953902958704</v>
+      </c>
+      <c r="K3" t="n">
+        <v>68</v>
+      </c>
+      <c r="L3" t="n">
+        <v>68</v>
+      </c>
+      <c r="M3" t="n">
+        <v>35.72367724482159</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4345258274181049</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.2495885023174792</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.09729143285886641</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MLOTST</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.09248244936484754</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ZSD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.06461484017841607</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.05804473584671273</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.05801905081092303</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UGO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.05706547756910977</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0548840297171134</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TOB</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.05296298006263581</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VGO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0492585031198231</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ZO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.04224024618083563</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.03646206462581342</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.03645555581363697</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.02605382617834012</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.01363353395768132</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.01094277139776548</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LAT</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
-      <c r="C22" t="n">
-        <v>8.766466663701067e-08</v>
-      </c>
-      <c r="D22" t="inlineStr">
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LON</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PROF</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:M24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>pearson_corr</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>r2_plot</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>mean_ssim</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>nrmse</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>mbe</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>w_dist</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>spearman_corr</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>hit_rate_percent</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>mean_yearly_hit_rate</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>mean_monthly_hit_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.2821869254112244</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.5607895255088806</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8221363764200855</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.259876161813736</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.501688801259721</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1305904285511926</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.01310920715332</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.08432938158512115</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5308513236964743</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4764012796668212</v>
+      </c>
+      <c r="K3" t="n">
+        <v>57.33333333333334</v>
+      </c>
+      <c r="L3" t="n">
+        <v>57.33333333333334</v>
+      </c>
+      <c r="M3" t="n">
+        <v>30.6259544437318</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Overall_Impact</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Significant_Grid_Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SPM</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1992134302854538</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2153225806451613</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1679299920797348</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1258602150537634</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ZSD</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1603610515594482</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.197741935483871</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1431343555450439</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.151505376344086</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MLOTST</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1311967819929123</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Positive (+)</t>
         </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.183494623655914</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UGO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1196667104959488</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1766666666666667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.1106145307421684</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1594623655913978</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VGO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.09138599783182144</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1999462365591398</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.06839382648468018</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2352688172043011</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ZO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0506184883415699</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1524193548387097</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.04717814922332764</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.04717814922332764</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TOB</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.04039588198065758</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3111290322580645</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.03795243799686432</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.009526642039418221</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.004063170403242111</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.177741935483871</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LON</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.325704476751177e-11</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Positive (+)</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LAT</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.175745265036277e-11</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PROF</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.113023128523905e-11</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Negative (-)</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1608,46 +2560,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5173675082777789</v>
+        <v>0.522214991545793</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7578703810206018</v>
+        <v>0.7592155861303864</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4826738493610659</v>
+        <v>0.4801472880517982</v>
       </c>
       <c r="D3" t="n">
-        <v>0.502981960773468</v>
+        <v>0.5086184740066528</v>
       </c>
       <c r="E3" t="n">
-        <v>1.904327931889335</v>
+        <v>1.894740415246401</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1947918766936014</v>
+        <v>0.1938111788167104</v>
       </c>
       <c r="G3" t="n">
-        <v>1.321373478588611</v>
+        <v>1.316458548849523</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5677882208851476</v>
+        <v>-0.5512412665597102</v>
       </c>
       <c r="I3" t="n">
-        <v>1.061260413258312</v>
+        <v>1.049557745666367</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7197255047219923</v>
+        <v>0.7196151413989975</v>
       </c>
       <c r="K3" t="n">
-        <v>48.66666666666667</v>
+        <v>46.33333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>48.66666666666667</v>
+        <v>46.33333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>34.68468468468468</v>
+        <v>35.01801801801802</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5528688855898922</v>
+        <v>0.5193165355195714</v>
       </c>
     </row>
     <row r="5">
@@ -1665,21 +2617,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2747600689837364</v>
+        <v>0.2779808348733862</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1933678796278239</v>
+        <v>0.1990519456060069</v>
       </c>
     </row>
     <row r="8">
@@ -1689,47 +2641,47 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1800818287535049</v>
+        <v>0.169393787104895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1451883060851044</v>
+        <v>0.146529975158319</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1389502834593309</v>
+        <v>0.1427167126839767</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0340271582768049</v>
+        <v>0.03225831426390958</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03362447481369475</v>
+        <v>0.03206843030950679</v>
       </c>
     </row>
   </sheetData>
@@ -1816,43 +2768,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5169064720072285</v>
+        <v>0.5201387690178164</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7585995926560705</v>
+        <v>0.7609970779839361</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4908296679578035</v>
+        <v>0.4849393501997674</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5024036765098572</v>
+        <v>0.5075852870941162</v>
       </c>
       <c r="E3" t="n">
-        <v>1.905237272529682</v>
+        <v>1.898852765169774</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1948848922750677</v>
+        <v>0.1942318271440181</v>
       </c>
       <c r="G3" t="n">
-        <v>1.306908830749982</v>
+        <v>1.303984406057416</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5901875208353563</v>
+        <v>-0.5876970956543772</v>
       </c>
       <c r="I3" t="n">
-        <v>1.044515209701142</v>
+        <v>1.039913932901602</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7219167655314058</v>
+        <v>0.7221659741730427</v>
       </c>
       <c r="K3" t="n">
-        <v>47</v>
+        <v>45.66666666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>47</v>
+        <v>45.66666666666666</v>
       </c>
       <c r="M3" t="n">
-        <v>34.75975975975976</v>
+        <v>34.94294294294294</v>
       </c>
     </row>
   </sheetData>
@@ -1939,43 +2891,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5037967521181721</v>
+        <v>0.5189053291228762</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7476911206978047</v>
+        <v>0.754679362352215</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4814770249423352</v>
+        <v>0.5286153616520102</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4915917813777924</v>
+        <v>0.5068457722663879</v>
       </c>
       <c r="E3" t="n">
-        <v>1.930915464478814</v>
+        <v>1.901291613614763</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1975114898878577</v>
+        <v>0.1944812946110522</v>
       </c>
       <c r="G3" t="n">
-        <v>1.298503291171964</v>
+        <v>1.27529525431077</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5968345033118563</v>
+        <v>-0.5691603752476266</v>
       </c>
       <c r="I3" t="n">
-        <v>1.034418863846348</v>
+        <v>1.002792462917292</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7145176856195021</v>
+        <v>0.7172669568194722</v>
       </c>
       <c r="K3" t="n">
-        <v>47</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="L3" t="n">
-        <v>47</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="M3" t="n">
-        <v>34.01801801801802</v>
+        <v>33.60960960960961</v>
       </c>
     </row>
   </sheetData>
@@ -1990,7 +2942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M12"/>
+  <dimension ref="A2:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -2059,46 +3011,54 @@
           <t>mean_monthly_hit_rate</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>val_r2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4239686877513599</v>
+        <v>0.4650128753431418</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6561383555925686</v>
+        <v>0.6932094181987202</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7759336260943714</v>
+        <v>0.8203671761985591</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4022642374038696</v>
+        <v>0.4059348404407501</v>
       </c>
       <c r="E3" t="n">
-        <v>1.284249405236245</v>
+        <v>1.296420654861705</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09861792595950197</v>
+        <v>0.1127398224978352</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7460346226224139</v>
+        <v>0.7346195547593555</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.09740234138441493</v>
+        <v>-0.1286493441260602</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4802822290250827</v>
+        <v>0.490719125460554</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5941096738544712</v>
+        <v>0.6325718041706949</v>
       </c>
       <c r="K3" t="n">
-        <v>64.33333333333333</v>
+        <v>69</v>
       </c>
       <c r="L3" t="n">
-        <v>64.44444444444444</v>
+        <v>69</v>
       </c>
       <c r="M3" t="n">
-        <v>30.36410264933322</v>
+        <v>37.23021086325829</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4140112919270137</v>
       </c>
     </row>
     <row r="5">
@@ -2116,21 +3076,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2655933461888232</v>
+        <v>0.2737852348327572</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2498551626693538</v>
+        <v>0.2462517275292811</v>
       </c>
     </row>
     <row r="8">
@@ -2140,47 +3100,47 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1551216285896718</v>
+        <v>0.1658660343104902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1398533618117629</v>
+        <v>0.1332163367362081</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1377725298054446</v>
+        <v>0.1269040319383976</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>MCOS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03077208364856796</v>
+        <v>0.02808322737781511</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>MSEN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02103188728637541</v>
+        <v>0.02589340727505073</v>
       </c>
     </row>
   </sheetData>
@@ -2267,43 +3227,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4096632260453719</v>
+        <v>0.4427168566693075</v>
       </c>
       <c r="B3" t="n">
-        <v>0.64318496770858</v>
+        <v>0.6715820884218445</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7489018891565367</v>
+        <v>0.7683927024482484</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4005488753318787</v>
+        <v>0.389288067817688</v>
       </c>
       <c r="E3" t="n">
-        <v>1.300098467131428</v>
+        <v>1.323159593554617</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09983498053327389</v>
+        <v>0.115065104180686</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7385428359545111</v>
+        <v>0.7427779971830405</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1005368884018129</v>
+        <v>-0.1230344014349617</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4553512309788286</v>
+        <v>0.4648837862261395</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5741879775451267</v>
+        <v>0.6096329304250239</v>
       </c>
       <c r="K3" t="n">
-        <v>63.55555555555556</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>63.44444444444444</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>31.58023602204054</v>
+        <v>36.28541003962638</v>
       </c>
     </row>
   </sheetData>
@@ -2390,43 +3350,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4168729008931139</v>
+        <v>0.4667219335262075</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6473475025736835</v>
+        <v>0.6879834666529271</v>
       </c>
       <c r="C3" t="n">
-        <v>0.79889737979831</v>
+        <v>0.8157595800156924</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4019865989685059</v>
+        <v>0.3891150951385498</v>
       </c>
       <c r="E3" t="n">
-        <v>1.292135146621226</v>
+        <v>1.294348239861222</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09922347458336662</v>
+        <v>0.1125596003620492</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7458760803199844</v>
+        <v>0.7359017133343664</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.07690508539921211</v>
+        <v>-0.1096989847447727</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4455049419331603</v>
+        <v>0.4345168623542931</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5667574044461284</v>
+        <v>0.5959122869591257</v>
       </c>
       <c r="K3" t="n">
-        <v>63.88888888888889</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>64</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>42.59934440615084</v>
+        <v>49.78768080783765</v>
       </c>
     </row>
   </sheetData>
@@ -2441,7 +3401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M12"/>
+  <dimension ref="A2:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -2513,43 +3473,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.2886205911636353</v>
+        <v>0.3454669713973999</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5599545240402222</v>
+        <v>0.5967980027198792</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7022079077214785</v>
+        <v>0.8235590113097808</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2666338682174683</v>
+        <v>0.2909184992313385</v>
       </c>
       <c r="E3" t="n">
-        <v>1.427174177782105</v>
+        <v>1.433969973224508</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1095931653321948</v>
+        <v>0.1247014382579412</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9324483275413513</v>
+        <v>0.9165326952934265</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0796208530664444</v>
+        <v>-0.1328138262033463</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5056556946677155</v>
+        <v>0.4928435041196644</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4647540018532914</v>
+        <v>0.4988626668541193</v>
       </c>
       <c r="K3" t="n">
-        <v>58.33333333333334</v>
+        <v>59.66666666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>57.11111111111111</v>
+        <v>59.66666666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>30.49133429253847</v>
+        <v>31.5387477872614</v>
       </c>
     </row>
     <row r="5">
@@ -2560,144 +3520,180 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Overall_Impact</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>Significant_Grid_Ratio</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Overall_Impact</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Direction</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3154301075268817</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.297783374786377</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.2550950050354004</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Negativa (-)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2173118279569893</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2151075268817204</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.4146672487258911</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.2256395369768143</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Negativa (-)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1360752688172043</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1934408602150538</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.5518999695777893</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Positive (+)</t>
-        </is>
+        <v>0.1963649690151215</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Negativa (-)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1716666666666667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2033333333333333</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.5607455372810364</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Positive (+)</t>
-        </is>
+        <v>0.1740487962961197</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Positiva (+)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1935483870967742</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1620967741935484</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7183315753936768</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.1653575003147125</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Positiva (+)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1753763440860215</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.1275649219751358</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.1267073303461075</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Negativa (-)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.204247311827957</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>0.09159847348928452</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Negativa (-)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2221505376344086</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.05866366252303123</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Positiva (+)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.1275649070739746</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.05866365879774094</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Negativa (-)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8333333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -2712,7 +3708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M12"/>
+  <dimension ref="A2:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -2784,43 +3780,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4662400484085083</v>
+        <v>0.4800191521644592</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6969954371452332</v>
+        <v>0.7060736417770386</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6510942185495402</v>
+        <v>0.6772860334777469</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4878996610641479</v>
+        <v>0.4929846525192261</v>
       </c>
       <c r="E3" t="n">
-        <v>2.002656483721252</v>
+        <v>1.976637948145463</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2048498099009879</v>
+        <v>0.2021883988652326</v>
       </c>
       <c r="G3" t="n">
-        <v>1.381198883056641</v>
+        <v>1.342345118522644</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3562632501125336</v>
+        <v>-0.3512311279773712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9261806139163673</v>
+        <v>0.8872732577013474</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6606190628956702</v>
+        <v>0.6655997662137727</v>
       </c>
       <c r="K3" t="n">
-        <v>43.33333333333334</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>43.33333333333334</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="M3" t="n">
-        <v>32.16816816816817</v>
+        <v>34.42642642642642</v>
       </c>
     </row>
     <row r="5">
@@ -2831,144 +3827,180 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Overall_Impact</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>Significant_Grid_Ratio</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Overall_Impact</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Direction</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2679569892473118</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.2257164120674133</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Positive (+)</t>
-        </is>
+        <v>0.2267097979784012</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Positiva (+)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2213978494623656</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vgo</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1528494623655914</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.3475975394248962</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Positive (+)</t>
-        </is>
+        <v>0.2170994728803635</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Negativa (-)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3269892473118279</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ugo</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1684408602150538</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.4798481464385986</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.1759504675865173</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Negativa (-)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1702688172043011</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mlotst</t>
+          <t>MLOTST</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2213978494623656</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.5326579213142395</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.1686103343963623</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Negativa (-)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2700537634408602</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2464516129032258</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.6727367043495178</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.1293241530656815</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Negativa (-)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1520430107526882</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>month_sin</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.06287206709384918</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.0938633531332016</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Negativa (-)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1399462365591398</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>month_cos</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.06287205964326859</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Negative (-)</t>
-        </is>
+        <v>0.07264820486307144</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Positiva (+)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2652688172043011</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.03894120082259178</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Negativa (-)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.03894120082259178</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Positiva (+)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8333333333333334</v>
       </c>
     </row>
   </sheetData>

--- a/modelado/modelos/resultados/Regre/ML_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/ML_reg.xlsx
@@ -2483,7 +2483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:N12"/>
+  <dimension ref="A2:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -2560,46 +2560,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.522214991545793</v>
+        <v>0.5280087224051035</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7592155861303864</v>
+        <v>0.7633814935332468</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4801472880517982</v>
+        <v>0.5046179915632705</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5086184740066528</v>
+        <v>0.5116494297981262</v>
       </c>
       <c r="E3" t="n">
-        <v>1.894740415246401</v>
+        <v>1.883217346908477</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1938111788167104</v>
+        <v>0.1926324952143615</v>
       </c>
       <c r="G3" t="n">
-        <v>1.316458548849523</v>
+        <v>1.306929754911692</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5512412665597102</v>
+        <v>-0.5512576664986647</v>
       </c>
       <c r="I3" t="n">
-        <v>1.049557745666367</v>
+        <v>1.047630752332242</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7196151413989975</v>
+        <v>0.7248835259755368</v>
       </c>
       <c r="K3" t="n">
-        <v>46.33333333333333</v>
+        <v>48</v>
       </c>
       <c r="L3" t="n">
-        <v>46.33333333333333</v>
+        <v>48</v>
       </c>
       <c r="M3" t="n">
-        <v>35.01801801801802</v>
+        <v>36.35135135135135</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5193165355195714</v>
+        <v>0.5185113863322373</v>
       </c>
     </row>
     <row r="5">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2779808348733862</v>
+        <v>0.2223529008727641</v>
       </c>
     </row>
     <row r="7">
@@ -2631,57 +2631,77 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1990519456060069</v>
+        <v>0.1530888724942968</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.169393787104895</v>
+        <v>0.1401719671178111</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UGO</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.146529975158319</v>
+        <v>0.1213609791639133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VGO</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1427167126839767</v>
+        <v>0.1050423561053488</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MSEN</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03225831426390958</v>
+        <v>0.1019788199772141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>VGO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.09951619876355461</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MSEN</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.02980498007573597</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>MCOS</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0.03206843030950679</v>
+      <c r="B14" t="n">
+        <v>0.0266829254293612</v>
       </c>
     </row>
   </sheetData>
@@ -2942,7 +2962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:N12"/>
+  <dimension ref="A2:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -3019,46 +3039,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4650128753431418</v>
+        <v>0.4853828472768393</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6932094181987202</v>
+        <v>0.7080019776843134</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8203671761985591</v>
+        <v>0.8266550754294942</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4059348404407501</v>
+        <v>0.3889884054660797</v>
       </c>
       <c r="E3" t="n">
-        <v>1.296420654861705</v>
+        <v>1.271500119777594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1127398224978352</v>
+        <v>0.1105726735162159</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7346195547593555</v>
+        <v>0.7318954544710977</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1286493441260602</v>
+        <v>-0.12464353550596</v>
       </c>
       <c r="I3" t="n">
-        <v>0.490719125460554</v>
+        <v>0.4727400726584609</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6325718041706949</v>
+        <v>0.6136598072306395</v>
       </c>
       <c r="K3" t="n">
-        <v>69</v>
+        <v>69.33333333333334</v>
       </c>
       <c r="L3" t="n">
-        <v>69</v>
+        <v>69.33333333333334</v>
       </c>
       <c r="M3" t="n">
-        <v>37.23021086325829</v>
+        <v>39.20157022102184</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4140112919270137</v>
+        <v>0.4324801930839407</v>
       </c>
     </row>
     <row r="5">
@@ -3080,7 +3100,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2737852348327572</v>
+        <v>0.2293855310054894</v>
       </c>
     </row>
     <row r="7">
@@ -3090,7 +3110,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2462517275292811</v>
+        <v>0.1790000283146898</v>
       </c>
     </row>
     <row r="8">
@@ -3100,47 +3120,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1658660343104902</v>
+        <v>0.1305681839349822</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UGO</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1332163367362081</v>
+        <v>0.1065325788659015</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VGO</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1269040319383976</v>
+        <v>0.1031604476939665</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MCOS</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02808322737781511</v>
+        <v>0.0918257929776486</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>VGO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.08637423677110034</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>MSEN</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0.02589340727505073</v>
+      <c r="B13" t="n">
+        <v>0.03935936303283758</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MCOS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0337938374033839</v>
       </c>
     </row>
   </sheetData>

--- a/modelado/modelos/resultados/Regre/ML_reg.xlsx
+++ b/modelado/modelos/resultados/Regre/ML_reg.xlsx
@@ -3038,7 +3038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I19"/>
+  <dimension ref="A2:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>mean_ssim</t>
+          <t>spearman_corr</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3080,58 +3080,48 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>w_dist</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>spearman_corr</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.508±0.004</t>
+          <t>0.527±0.006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.718±0.002</t>
+          <t>0.736±0.003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.394±0.004</t>
+          <t>0.638±0.004</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.244±0.005</t>
+          <t>1.220±0.008</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.108±0.000</t>
+          <t>0.106±0.001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.745±0.001</t>
+          <t>0.728±0.002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.023±0.003</t>
+          <t>-0.033±0.021</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.480±0.004</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.616±0.000</t>
+          <t>0.492±0.006</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3145,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.294±0.009</t>
+          <t>0.293±0.002</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3157,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.109±0.002</t>
+          <t>0.107±0.002</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3169,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.089±0.001</t>
+          <t>0.092±0.009</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3181,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.073±0.002</t>
+          <t>0.064±0.002</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3193,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.063±0.006</t>
+          <t>0.061±0.004</t>
         </is>
       </c>
     </row>
@@ -3215,43 +3205,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.062±0.001</t>
+          <t>0.060±0.004</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UGO</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.054±0.001</t>
+          <t>0.055±0.004</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VGO</t>
+          <t>UGO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.051±0.002</t>
+          <t>0.054±0.007</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>VGO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.046±0.000</t>
+          <t>0.052±0.003</t>
         </is>
       </c>
     </row>
@@ -3263,31 +3253,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.045±0.000</t>
+          <t>0.051±0.002</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TOB</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.043±0.001</t>
+          <t>0.045±0.001</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>TOB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.042±0.000</t>
+          <t>0.044±0.005</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3289,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.015±0.000</t>
+          <t>0.012±0.003</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3301,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.014±0.004</t>
+          <t>0.012±0.000</t>
         </is>
       </c>
     </row>
